--- a/data/tickets/ams_tickets.xlsx
+++ b/data/tickets/ams_tickets.xlsx
@@ -10,15 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ServiceNow" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JIRA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mailbox" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ground_Truth" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Dictionary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Dictionary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ServiceNow'!$A$1:$W$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JIRA'!$A$1:$Q$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mailbox'!$A$1:$L$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ground_Truth'!$A$1:$J$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data_Dictionary'!$A$1:$C$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data_Dictionary'!$A$1:$C$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2773,11 +2771,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2866,11 +2859,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2909,8 +2897,6 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>EmployeePortal</t>
@@ -2951,11 +2937,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2994,9 +2975,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>VPN not connecting from home</t>
@@ -3032,11 +3010,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3075,9 +3048,6 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Laptop screen flickering</t>
@@ -3113,11 +3083,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3156,8 +3121,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>InsightBI</t>
@@ -3198,11 +3161,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -3241,8 +3199,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>OrderHub</t>
@@ -3283,11 +3239,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3376,11 +3327,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -3469,11 +3415,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3562,11 +3503,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -3655,11 +3591,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -3698,8 +3629,6 @@
           <t>Chat</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>BillingEngine</t>
@@ -3740,11 +3669,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
@@ -3833,11 +3757,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
@@ -3926,11 +3845,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -3969,9 +3883,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>System not working</t>
@@ -4007,11 +3918,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -4100,11 +4006,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
@@ -4193,11 +4094,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -4286,11 +4182,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
@@ -4379,11 +4270,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
@@ -4422,8 +4308,6 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>SalesConnect CRM</t>
@@ -4464,11 +4348,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
@@ -4507,9 +4386,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Access</t>
@@ -4545,11 +4421,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -4588,9 +4459,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Report wrong</t>
@@ -4626,11 +4494,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -4719,11 +4582,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
@@ -4812,11 +4670,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
@@ -4905,11 +4758,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
@@ -4948,9 +4796,6 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
           <t>Test</t>
@@ -4986,11 +4831,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
@@ -5079,11 +4919,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
@@ -5172,11 +5007,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -5265,11 +5095,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
@@ -5358,11 +5183,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
@@ -5451,11 +5271,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
@@ -5544,11 +5359,6 @@
           <t>New</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5728,7 +5538,6 @@
           <t>PayrollPro</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Production</t>
@@ -5985,7 +5794,6 @@
           <t>InsightBI</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6068,7 +5876,6 @@
           <t>SalesConnect CRM</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6151,7 +5958,6 @@
           <t>EmployeePortal</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6234,7 +6040,6 @@
           <t>EmployeePortal</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6317,7 +6122,6 @@
           <t>PayrollPro</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6400,7 +6204,6 @@
           <t>StockSense</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6483,7 +6286,6 @@
           <t>BillingEngine</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6566,7 +6368,6 @@
           <t>InsightBI</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6649,7 +6450,6 @@
           <t>EmployeePortal</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6732,7 +6532,6 @@
           <t>InsightBI</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6815,7 +6614,6 @@
           <t>StockSense</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6898,7 +6696,6 @@
           <t>BillingEngine</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Production</t>
@@ -6976,16 +6773,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -7039,16 +6831,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -7102,16 +6889,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -7170,19 +6952,16 @@
           <t>EmployeePortal</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -7241,19 +7020,16 @@
           <t>PayrollPro</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -7312,19 +7088,16 @@
           <t>SalesConnect CRM</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -7393,13 +7166,11 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -7458,19 +7229,16 @@
           <t>SalesConnect CRM</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -7529,19 +7297,16 @@
           <t>SalesConnect CRM</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -7600,19 +7365,16 @@
           <t>StockSense</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7671,19 +7433,16 @@
           <t>SalesConnect CRM</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -7742,19 +7501,16 @@
           <t>BillingEngine</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -7813,19 +7569,16 @@
           <t>OrderHub</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -7894,13 +7647,11 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -7954,16 +7705,11 @@
           <t>Highest</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -8088,7 +7834,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Everything is slow</t>
@@ -8109,7 +7854,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8142,7 +7886,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Orders not shipped - new product</t>
@@ -8167,7 +7910,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8283,7 +8025,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8345,7 +8086,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8407,7 +8147,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8469,7 +8208,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8502,7 +8240,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Invoice issue</t>
@@ -8523,7 +8260,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8556,7 +8292,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>FW: Double charge for customer order ORD-4122394</t>
@@ -8581,7 +8316,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8614,7 +8348,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Overtime not paid</t>
@@ -8639,7 +8372,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8672,7 +8404,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Scanner problem</t>
@@ -8697,7 +8428,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8730,7 +8460,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>cant login</t>
@@ -8751,7 +8480,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8784,7 +8512,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Labels not printing Pune</t>
@@ -8809,7 +8536,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8909,7 +8635,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>RE: Labels not printing Chennai</t>
@@ -8934,7 +8659,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8967,7 +8691,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Can't receive goods - PO locked</t>
@@ -8992,7 +8715,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9025,7 +8747,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Website checkout down!!</t>
@@ -9117,7 +8838,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9212,7 +8932,6 @@
           <t>ams-support@contoso.com</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>No order confirmation mails to customers</t>
@@ -9237,7 +8956,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L21"/>
@@ -9251,4020 +8969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ticket_ref</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dq_should_pass</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>expected_application</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>expected_kb_article</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>reported_priority</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>expected_priority</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>missing_information</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INC0010231</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>KB-PAY-001</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AMS-1187</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KB-PAY-005</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INC0010232</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KB-BI-003</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INC0010233</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KB-ORD-003</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>INC0010234</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KB-BI-003</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AMS-1188</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KB-PAY-004</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INC0010235</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KB-PAY-003</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AMS-1189</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KB-PAY-004</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>INC0010236</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KB-ORD-005</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INC0010237</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KB-EMP-004</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INC0010238</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KB-BIL-002</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AMS-1190</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KB-BI-001</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AMS-1191</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KB-CRM-004</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INC0010239</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KB-ORD-005</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AMS-1192</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KB-EMP-003</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>INC0010240</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KB-BIL-005</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AMS-1193</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KB-EMP-001</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AMS-1194</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KB-PAY-001</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AMS-1195</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KB-STK-002</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>INC0010241</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>KB-EMP-003</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>INC0010242</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KB-ORD-004</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>INC0010243</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>KB-STK-001</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AMS-1196</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KB-BIL-003</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AMS-1197</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KB-BI-001</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>INC0010244</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>KB-CRM-002</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AMS-1198</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KB-EMP-004</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>INC0010245</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KB-ORD-001</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>INC0010246</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KB-PAY-005</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AMS-1199</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KB-BI-002</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>INC0010247</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>KB-ORD-001</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>INC0010248</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KB-EMP-002</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AMS-1200</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KB-STK-004</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AMS-1201</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KB-BIL-003</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>4</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>INC0010249</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KB-PAY-003</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>INC0010250</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KB-BIL-004</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Reported P1 but expected P4 (over-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>INC0010251</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Broken intranet link; not in KB (do not confuse with KB-PAY-001).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>INC0010252</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Out of AMS scope (network/infrastructure).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>INC0010253</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Out of AMS scope (end-user hardware).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MBX-00001</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>application, since when, how many users</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Borderline - application can be inferred but key details missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>INC0010254</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Feature request, not an incident.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AMS-1202</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>reference to previous ticket, application, symptom</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>INC0010255</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Address service data gap; not in KB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>INC0010256</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>KB-BI-001</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MBX-00002</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>KB-ORD-005</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MBX-00003</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>everything - empty forwarded email with attachment only</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MBX-00004</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>application, problem description</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MBX-00005</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Real P1 defect in OrderHub; no KB article covers promotions/pricing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>INC0010257</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>KB-ORD-004</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>INC0010258</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KB-EMP-002</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>INC0010259</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>KB-STK-005</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" t="n">
-        <v>4</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>Reported P2 but expected P4 (over-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MBX-00006</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>KB-STK-001</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>INC0010260</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>4</v>
-      </c>
-      <c r="H53" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Template change request; not in KB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>INC0010261</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>KB-ORD-001</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>INC0010262</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>KB-BIL-003</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" t="n">
-        <v>4</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>INC0010263</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>application, symptom/error, impact</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MBX-00007</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>KB-BI-002</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>3</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>INC0010264</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>KB-EMP-003</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>4</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>INC0010265</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KB-EMP-005</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>5</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Reported P1 but expected P5 (over-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>INC0010266</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>KB-BIL-005</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" t="n">
-        <v>3</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MBX-00008</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>invoice number, customer, nature of complaint (application inferable: BillingEngine)</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Borderline - application can be inferred but key details missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>INC0010267</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KB-PAY-002</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>4</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>Reported P4 but expected P1 (under-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MBX-00009</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>KB-ORD-004</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
-        <v>3</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MBX-00010</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>KB-PAY-005</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>AMS-1203</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>3</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>symptom, error, affected orders</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>AMS-1204</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
-        <v>3</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>what is wrong with salary, period, employee ID</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MBX-00011</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>device ID, error message, site (application inferable: StockSense)</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>Borderline - application can be inferred but key details missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MBX-00012</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>application, error message</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MBX-00013</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>KB-STK-003</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="n">
-        <v>3</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>INC0010268</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="n">
-        <v>3</v>
-      </c>
-      <c r="H70" t="n">
-        <v>3</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Mobile client defect; not in KB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>INC0010269</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="n">
-        <v>3</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>application, role/permission, approval</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>INC0010270</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="n">
-        <v>3</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>report name, which numbers, expected values</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>INC0010271</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>KB-BI-005</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>2</v>
-      </c>
-      <c r="H73" t="n">
-        <v>4</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Reported P2 but expected P4 (over-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MBX-00014</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>KB-BIL-001</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>4</v>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Reported P4 but expected P1 (under-prioritised by user) - implied by email tone/importance flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>INC0010272</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>KB-PAY-001</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>3</v>
-      </c>
-      <c r="H75" t="n">
-        <v>3</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MBX-00015</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>KB-STK-003</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="n">
-        <v>3</v>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>AMS-1205</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>KB-EMP-004</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>3</v>
-      </c>
-      <c r="H77" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>AMS-1206</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Employee master sync gap; not covered by KB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>INC0010273</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>KB-BI-002</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H79" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>INC0010274</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="n">
-        <v>3</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>not a real incident</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AMS-1207</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>KB-CRM-004</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>3</v>
-      </c>
-      <c r="H81" t="n">
-        <v>3</v>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>INC0010275</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>KB-BI-003</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>4</v>
-      </c>
-      <c r="H82" t="n">
-        <v>4</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>MBX-00016</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>KB-STK-004</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>MBX-00017</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>related_duplicate</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>KB-ORD-003</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Checkout outage incident storm; related tickets: INC0010276, AMS-1208, INC0010277</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>INC0010276</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>KB-ORD-003</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>Checkout outage incident storm; related tickets: MBX-00017, AMS-1208, INC0010277</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>AMS-1208</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>related_duplicate</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>KB-ORD-003</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>Checkout outage incident storm; related tickets: MBX-00017, INC0010276, INC0010277</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>INC0010277</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>related_duplicate</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>KB-ORD-003</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>Checkout outage incident storm; related tickets: MBX-00017, INC0010276, AMS-1208</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AMS-1209</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>KB-CRM-001</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>3</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>Reported P1 but expected P3 (over-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>MBX-00018</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>InsightBI</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>KB-BI-004</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>4</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>Reported P1 but expected P4 (over-prioritised by user) - implied by email tone/importance flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>INC0010278</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>KB-CRM-003</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>2</v>
-      </c>
-      <c r="H90" t="n">
-        <v>4</v>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>Reported P2 but expected P4 (over-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>AMS-1210</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>KB-CRM-002</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>2</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>INC0010279</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>KB-STK-002</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>2</v>
-      </c>
-      <c r="H92" t="n">
-        <v>2</v>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>INC0010280</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>EmployeePortal</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>KB-EMP-001</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="n">
-        <v>1</v>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>MBX-00019</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>application, error text (screenshot only)</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AMS-1211</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>no_kb_match</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>StockSense</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="n">
-        <v>3</v>
-      </c>
-      <c r="H95" t="n">
-        <v>3</v>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Barcode/item master data issue; not in KB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>AMS-1212</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>priority_mismatch</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>SalesConnect CRM</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>KB-CRM-005</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>4</v>
-      </c>
-      <c r="H96" t="n">
-        <v>2</v>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>Reported P4 but expected P2 (under-prioritised by user)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>AMS-1213</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>BillingEngine</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>KB-BIL-002</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>3</v>
-      </c>
-      <c r="H97" t="n">
-        <v>3</v>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>AMS-1214</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>KB-ORD-002</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>3</v>
-      </c>
-      <c r="H98" t="n">
-        <v>3</v>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>AMS-1215</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>PayrollPro</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>KB-PAY-004</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" t="n">
-        <v>1</v>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>AMS-1216</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>JIRA</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>application, problem description</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>MBX-00020</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Mailbox</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>OrderHub</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>KB-ORD-002</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="n">
-        <v>3</v>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J101"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13544,57 +9249,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ground_Truth</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>EVALUATION ONLY - agents must not read this sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ground_Truth</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>complete, incomplete, priority_mismatch, no_kb_match, related_duplicate</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ground_Truth</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>expected_priority</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Draft expected priority (1-5) from KB impact/urgency; to be validated against the rulebook</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:C19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
